--- a/artfynd/A 26948-2024 artfynd.xlsx
+++ b/artfynd/A 26948-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118621891</v>
+        <v>118623324</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565134</v>
+        <v>565410</v>
       </c>
       <c r="R2" t="n">
-        <v>7060977</v>
+        <v>7061035</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118621670</v>
+        <v>118621971</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565247</v>
+        <v>565098</v>
       </c>
       <c r="R3" t="n">
-        <v>7061001</v>
+        <v>7060988</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118623324</v>
+        <v>118621853</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565410</v>
+        <v>565182</v>
       </c>
       <c r="R4" t="n">
-        <v>7061035</v>
+        <v>7060974</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118621971</v>
+        <v>118621891</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565098</v>
+        <v>565134</v>
       </c>
       <c r="R5" t="n">
-        <v>7060988</v>
+        <v>7060977</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118621853</v>
+        <v>118621670</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565182</v>
+        <v>565247</v>
       </c>
       <c r="R6" t="n">
-        <v>7060974</v>
+        <v>7061001</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118621901</v>
+        <v>118623299</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565130</v>
+        <v>565430</v>
       </c>
       <c r="R7" t="n">
-        <v>7060967</v>
+        <v>7061018</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118623299</v>
+        <v>118621901</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565430</v>
+        <v>565130</v>
       </c>
       <c r="R8" t="n">
-        <v>7061018</v>
+        <v>7060967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:48</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:48</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 26948-2024 artfynd.xlsx
+++ b/artfynd/A 26948-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118623324</v>
+        <v>118621891</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565410</v>
+        <v>565134</v>
       </c>
       <c r="R2" t="n">
-        <v>7061035</v>
+        <v>7060977</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118621971</v>
+        <v>118623299</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565098</v>
+        <v>565430</v>
       </c>
       <c r="R3" t="n">
-        <v>7060988</v>
+        <v>7061018</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118621853</v>
+        <v>118621670</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565182</v>
+        <v>565247</v>
       </c>
       <c r="R4" t="n">
-        <v>7060974</v>
+        <v>7061001</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118621891</v>
+        <v>118621901</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565134</v>
+        <v>565130</v>
       </c>
       <c r="R5" t="n">
-        <v>7060977</v>
+        <v>7060967</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118621670</v>
+        <v>118623324</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565247</v>
+        <v>565410</v>
       </c>
       <c r="R6" t="n">
-        <v>7061001</v>
+        <v>7061035</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118623299</v>
+        <v>118621971</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565430</v>
+        <v>565098</v>
       </c>
       <c r="R7" t="n">
-        <v>7061018</v>
+        <v>7060988</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:48</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:48</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118621901</v>
+        <v>118621853</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565130</v>
+        <v>565182</v>
       </c>
       <c r="R8" t="n">
-        <v>7060967</v>
+        <v>7060974</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 26948-2024 artfynd.xlsx
+++ b/artfynd/A 26948-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118621891</v>
+        <v>118623299</v>
       </c>
       <c r="B2" t="n">
         <v>57290</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565134</v>
+        <v>565430</v>
       </c>
       <c r="R2" t="n">
-        <v>7060977</v>
+        <v>7061018</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118623299</v>
+        <v>118623324</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565430</v>
+        <v>565410</v>
       </c>
       <c r="R3" t="n">
-        <v>7061018</v>
+        <v>7061035</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:48</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:48</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118621670</v>
+        <v>118621853</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565247</v>
+        <v>565182</v>
       </c>
       <c r="R4" t="n">
-        <v>7061001</v>
+        <v>7060974</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118623324</v>
+        <v>118621891</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565410</v>
+        <v>565134</v>
       </c>
       <c r="R6" t="n">
-        <v>7061035</v>
+        <v>7060977</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118621853</v>
+        <v>118621670</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565182</v>
+        <v>565247</v>
       </c>
       <c r="R8" t="n">
-        <v>7060974</v>
+        <v>7061001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 26948-2024 artfynd.xlsx
+++ b/artfynd/A 26948-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118623324</v>
+        <v>118621901</v>
       </c>
       <c r="B3" t="n">
         <v>57290</v>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565410</v>
+        <v>565130</v>
       </c>
       <c r="R3" t="n">
-        <v>7061035</v>
+        <v>7060967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118621853</v>
+        <v>118623324</v>
       </c>
       <c r="B4" t="n">
         <v>57290</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565182</v>
+        <v>565410</v>
       </c>
       <c r="R4" t="n">
-        <v>7060974</v>
+        <v>7061035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118621901</v>
+        <v>118621853</v>
       </c>
       <c r="B5" t="n">
         <v>57290</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565130</v>
+        <v>565182</v>
       </c>
       <c r="R5" t="n">
-        <v>7060967</v>
+        <v>7060974</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118621891</v>
+        <v>118621971</v>
       </c>
       <c r="B6" t="n">
         <v>57290</v>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565134</v>
+        <v>565098</v>
       </c>
       <c r="R6" t="n">
-        <v>7060977</v>
+        <v>7060988</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118621971</v>
+        <v>118621670</v>
       </c>
       <c r="B7" t="n">
         <v>57290</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565098</v>
+        <v>565247</v>
       </c>
       <c r="R7" t="n">
-        <v>7060988</v>
+        <v>7061001</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1377,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118621670</v>
+        <v>118621891</v>
       </c>
       <c r="B8" t="n">
         <v>57290</v>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565247</v>
+        <v>565134</v>
       </c>
       <c r="R8" t="n">
-        <v>7061001</v>
+        <v>7060977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 26948-2024 artfynd.xlsx
+++ b/artfynd/A 26948-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AY108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118621891</v>
+        <v>119204686</v>
       </c>
       <c r="B2" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565134</v>
+        <v>565142</v>
       </c>
       <c r="R2" t="n">
-        <v>7060977</v>
+        <v>7061019</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118621901</v>
+        <v>132120233</v>
       </c>
       <c r="B3" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565130</v>
+        <v>565380</v>
       </c>
       <c r="R3" t="n">
-        <v>7060967</v>
+        <v>7061037</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>22:06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>22:06</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118621971</v>
+        <v>132120471</v>
       </c>
       <c r="B4" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,42 +890,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565098</v>
+        <v>565365</v>
       </c>
       <c r="R4" t="n">
-        <v>7060988</v>
+        <v>7061069</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>22:11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>22:11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118623324</v>
+        <v>132120206</v>
       </c>
       <c r="B5" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,42 +987,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565410</v>
+        <v>565423</v>
       </c>
       <c r="R5" t="n">
-        <v>7061035</v>
+        <v>7061009</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,22 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>23:50</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>23:50</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,27 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118623299</v>
+        <v>132120238</v>
       </c>
       <c r="B6" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1159,42 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565430</v>
+        <v>565382</v>
       </c>
       <c r="R6" t="n">
-        <v>7061018</v>
+        <v>7061041</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,22 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>23:48</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>23:48</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,27 +1158,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118621853</v>
+        <v>132120493</v>
       </c>
       <c r="B7" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,42 +1181,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565182</v>
+        <v>565381</v>
       </c>
       <c r="R7" t="n">
-        <v>7060974</v>
+        <v>7061032</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,22 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>22:01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>22:01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,27 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118621670</v>
+        <v>132126693</v>
       </c>
       <c r="B8" t="n">
-        <v>57292</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,42 +1278,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565247</v>
+        <v>564952</v>
       </c>
       <c r="R8" t="n">
-        <v>7061001</v>
+        <v>7061172</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,22 +1332,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>21:52</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>21:52</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,27 +1352,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119149743</v>
+        <v>132120301</v>
       </c>
       <c r="B9" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,42 +1375,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>565387</v>
+        <v>565389</v>
       </c>
       <c r="R9" t="n">
-        <v>7061007</v>
+        <v>7061042</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,22 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>21:13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>21:13</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,27 +1449,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119149694</v>
+        <v>132120483</v>
       </c>
       <c r="B10" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1627,42 +1472,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>565380</v>
+        <v>565376</v>
       </c>
       <c r="R10" t="n">
-        <v>7061004</v>
+        <v>7061044</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,22 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>21:10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>21:10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,65 +1546,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119203593</v>
+        <v>132122995</v>
       </c>
       <c r="B11" t="n">
-        <v>91842</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83222</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>565254</v>
+        <v>565282</v>
       </c>
       <c r="R11" t="n">
-        <v>7061019</v>
+        <v>7061075</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,22 +1623,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,65 +1653,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119204501</v>
+        <v>132127333</v>
       </c>
       <c r="B12" t="n">
-        <v>58164</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83222</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208249</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>565147</v>
+        <v>565032</v>
       </c>
       <c r="R12" t="n">
-        <v>7060991</v>
+        <v>7061107</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1910,22 +1730,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1940,27 +1750,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119204963</v>
+        <v>119219132</v>
       </c>
       <c r="B13" t="n">
-        <v>79142</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,37 +1773,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>565053</v>
+        <v>565014</v>
       </c>
       <c r="R13" t="n">
-        <v>7061049</v>
+        <v>7060973</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,19 +1830,9 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,15 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119203918</v>
+        <v>119208820</v>
       </c>
       <c r="B14" t="n">
-        <v>78261</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,34 +1870,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>565151</v>
+        <v>565038</v>
       </c>
       <c r="R14" t="n">
-        <v>7061004</v>
+        <v>7060976</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2137,9 +1927,19 @@
           <t>2024-08-18</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,27 +1954,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119204357</v>
+        <v>119219142</v>
       </c>
       <c r="B15" t="n">
-        <v>79142</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2182,37 +1977,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>565153</v>
+        <v>565039</v>
       </c>
       <c r="R15" t="n">
-        <v>7060971</v>
+        <v>7060972</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2239,19 +2034,9 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,27 +2051,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119204873</v>
+        <v>119219143</v>
       </c>
       <c r="B16" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,37 +2074,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>565048</v>
+        <v>565023</v>
       </c>
       <c r="R16" t="n">
-        <v>7061035</v>
+        <v>7060965</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2368,65 +2148,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119204231</v>
+        <v>119203593</v>
       </c>
       <c r="B17" t="n">
-        <v>79641</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>565199</v>
+        <v>565254</v>
       </c>
       <c r="R17" t="n">
-        <v>7060966</v>
+        <v>7061019</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2492,53 +2267,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119204967</v>
+        <v>119203597</v>
       </c>
       <c r="B18" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>565052</v>
+        <v>565252</v>
       </c>
       <c r="R18" t="n">
-        <v>7061050</v>
+        <v>7061021</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,19 +2335,9 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,65 +2352,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119204686</v>
+        <v>119219135</v>
       </c>
       <c r="B19" t="n">
-        <v>78558</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6276</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>565142</v>
+        <v>565049</v>
       </c>
       <c r="R19" t="n">
-        <v>7061019</v>
+        <v>7060968</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2677,19 +2432,9 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,19 +2461,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119204561</v>
+        <v>119204162</v>
       </c>
       <c r="B20" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2752,14 +2492,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>565103</v>
+        <v>565209</v>
       </c>
       <c r="R20" t="n">
-        <v>7061011</v>
+        <v>7060969</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2789,9 +2529,19 @@
           <t>2024-08-18</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2806,62 +2556,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119208820</v>
+        <v>119204561</v>
       </c>
       <c r="B21" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>565038</v>
+        <v>565103</v>
       </c>
       <c r="R21" t="n">
-        <v>7060976</v>
+        <v>7061011</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2891,19 +2636,9 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>18:32</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>18:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,70 +2653,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Hillevi Nydahl</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119205327</v>
+        <v>119204873</v>
       </c>
       <c r="B22" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>565047</v>
+        <v>565048</v>
       </c>
       <c r="R22" t="n">
-        <v>7061046</v>
+        <v>7061035</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3008,19 +2733,9 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:34</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3035,62 +2750,60 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119204425</v>
+        <v>119213719</v>
       </c>
       <c r="B23" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>565136</v>
+        <v>565151</v>
       </c>
       <c r="R23" t="n">
-        <v>7060972</v>
+        <v>7061009</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3120,97 +2833,78 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119204908</v>
+        <v>132120876</v>
       </c>
       <c r="B24" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>565046</v>
+        <v>565379</v>
       </c>
       <c r="R24" t="n">
-        <v>7061046</v>
+        <v>7061167</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3234,12 +2928,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,15 +2960,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119203597</v>
+        <v>132121251</v>
       </c>
       <c r="B25" t="n">
-        <v>91842</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3282,37 +2971,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>565252</v>
+        <v>565427</v>
       </c>
       <c r="R25" t="n">
-        <v>7061021</v>
+        <v>7061070</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3336,12 +3025,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,31 +3055,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119213719</v>
+        <v>132121843</v>
       </c>
       <c r="B26" t="n">
-        <v>78524</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3402,19 +3096,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottran, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>565151</v>
+        <v>565430</v>
       </c>
       <c r="R26" t="n">
-        <v>7061009</v>
+        <v>7061164</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3441,12 +3132,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,72 +3156,66 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119204924</v>
+        <v>132121965</v>
       </c>
       <c r="B27" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>565083</v>
+        <v>565402</v>
       </c>
       <c r="R27" t="n">
-        <v>7061046</v>
+        <v>7061164</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3544,22 +3239,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3574,70 +3259,60 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119204938</v>
+        <v>132122130</v>
       </c>
       <c r="B28" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ottran (Ottran), Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>565056</v>
+        <v>565382</v>
       </c>
       <c r="R28" t="n">
-        <v>7061039</v>
+        <v>7061115</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3661,12 +3336,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3693,53 +3368,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119219142</v>
+        <v>132122865</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottran, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>565039</v>
+        <v>565271</v>
       </c>
       <c r="R29" t="n">
-        <v>7060972</v>
+        <v>7061139</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3763,12 +3433,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3783,27 +3453,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119219135</v>
+        <v>132123121</v>
       </c>
       <c r="B30" t="n">
-        <v>89250</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3811,37 +3476,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6276</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottran, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565049</v>
+        <v>565302</v>
       </c>
       <c r="R30" t="n">
-        <v>7060968</v>
+        <v>7061034</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3865,12 +3530,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3885,65 +3550,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119219137</v>
+        <v>132124552</v>
       </c>
       <c r="B31" t="n">
-        <v>78260</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ottran, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565042</v>
+        <v>565189</v>
       </c>
       <c r="R31" t="n">
-        <v>7061038</v>
+        <v>7061025</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3967,12 +3627,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3987,65 +3647,60 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119219143</v>
+        <v>132125044</v>
       </c>
       <c r="B32" t="n">
-        <v>91838</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ottran, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565023</v>
+        <v>565041</v>
       </c>
       <c r="R32" t="n">
-        <v>7060965</v>
+        <v>7061062</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4069,12 +3724,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4089,26 +3744,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132127840</v>
+        <v>132125276</v>
       </c>
       <c r="B33" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4136,10 +3791,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565124</v>
+        <v>565040</v>
       </c>
       <c r="R33" t="n">
-        <v>7061052</v>
+        <v>7061090</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4198,32 +3853,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132121316</v>
+        <v>132125526</v>
       </c>
       <c r="B34" t="n">
-        <v>83311</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4233,10 +3888,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>565265</v>
+        <v>564999</v>
       </c>
       <c r="R34" t="n">
-        <v>7061075</v>
+        <v>7061122</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4295,14 +3950,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132123121</v>
+        <v>132126348</v>
       </c>
       <c r="B35" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4326,14 +3981,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>565302</v>
+        <v>564994</v>
       </c>
       <c r="R35" t="n">
-        <v>7061034</v>
+        <v>7061131</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4392,14 +4047,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132128016</v>
+        <v>132126475</v>
       </c>
       <c r="B36" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4423,14 +4078,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>565168</v>
+        <v>564979</v>
       </c>
       <c r="R36" t="n">
-        <v>7061024</v>
+        <v>7061150</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4489,45 +4144,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132127333</v>
+        <v>132126678</v>
       </c>
       <c r="B37" t="n">
-        <v>83177</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>565032</v>
+        <v>564952</v>
       </c>
       <c r="R37" t="n">
-        <v>7061107</v>
+        <v>7061172</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4586,45 +4241,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132120206</v>
+        <v>132126749</v>
       </c>
       <c r="B38" t="n">
-        <v>91913</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>565423</v>
+        <v>564932</v>
       </c>
       <c r="R38" t="n">
-        <v>7061009</v>
+        <v>7061188</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4683,50 +4338,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132123180</v>
+        <v>132126937</v>
       </c>
       <c r="B39" t="n">
-        <v>57954</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>565295</v>
+        <v>565003</v>
       </c>
       <c r="R39" t="n">
-        <v>7061029</v>
+        <v>7061162</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4759,11 +4409,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4790,14 +4435,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132125276</v>
+        <v>132127049</v>
       </c>
       <c r="B40" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4821,14 +4466,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>565040</v>
+        <v>565015</v>
       </c>
       <c r="R40" t="n">
-        <v>7061090</v>
+        <v>7061153</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4887,45 +4532,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132120493</v>
+        <v>132127097</v>
       </c>
       <c r="B41" t="n">
-        <v>91913</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>565381</v>
+        <v>565020</v>
       </c>
       <c r="R41" t="n">
-        <v>7061032</v>
+        <v>7061146</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4984,50 +4629,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132123234</v>
+        <v>132127354</v>
       </c>
       <c r="B42" t="n">
-        <v>57954</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>565315</v>
+        <v>565022</v>
       </c>
       <c r="R42" t="n">
-        <v>7061025</v>
+        <v>7061116</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5060,11 +4700,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5091,14 +4726,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132127939</v>
+        <v>132127468</v>
       </c>
       <c r="B43" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5126,10 +4761,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>565123</v>
+        <v>565050</v>
       </c>
       <c r="R43" t="n">
-        <v>7061050</v>
+        <v>7061109</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5188,14 +4823,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132126678</v>
+        <v>132127840</v>
       </c>
       <c r="B44" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5219,14 +4854,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>564952</v>
+        <v>565124</v>
       </c>
       <c r="R44" t="n">
-        <v>7061172</v>
+        <v>7061052</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5285,14 +4920,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132127049</v>
+        <v>132127939</v>
       </c>
       <c r="B45" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5316,14 +4951,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>565015</v>
+        <v>565123</v>
       </c>
       <c r="R45" t="n">
-        <v>7061153</v>
+        <v>7061050</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5382,50 +5017,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132123408</v>
+        <v>132128016</v>
       </c>
       <c r="B46" t="n">
-        <v>57954</v>
+        <v>79373</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565387</v>
+        <v>565168</v>
       </c>
       <c r="R46" t="n">
-        <v>7060982</v>
+        <v>7061024</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5458,11 +5088,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5489,50 +5114,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132127502</v>
+        <v>132128160</v>
       </c>
       <c r="B47" t="n">
-        <v>57951</v>
+        <v>79373</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>565078</v>
+        <v>565220</v>
       </c>
       <c r="R47" t="n">
-        <v>7061092</v>
+        <v>7060999</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5591,10 +5211,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132128160</v>
+        <v>132121002</v>
       </c>
       <c r="B48" t="n">
-        <v>79329</v>
+        <v>83358</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5602,21 +5222,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5626,10 +5246,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>565220</v>
+        <v>565348</v>
       </c>
       <c r="R48" t="n">
-        <v>7060999</v>
+        <v>7061074</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5688,10 +5308,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132121523</v>
+        <v>132121316</v>
       </c>
       <c r="B49" t="n">
-        <v>57954</v>
+        <v>83358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5699,46 +5319,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>565420</v>
+        <v>565265</v>
       </c>
       <c r="R49" t="n">
-        <v>7061119</v>
+        <v>7061075</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5765,19 +5376,9 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5792,22 +5393,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132127761</v>
+        <v>132122939</v>
       </c>
       <c r="B50" t="n">
-        <v>57954</v>
+        <v>83358</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5815,39 +5416,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>565110</v>
+        <v>565315</v>
       </c>
       <c r="R50" t="n">
-        <v>7061072</v>
+        <v>7061039</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5880,11 +5476,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5911,10 +5502,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132123395</v>
+        <v>132125187</v>
       </c>
       <c r="B51" t="n">
-        <v>57954</v>
+        <v>83358</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5922,39 +5513,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>565388</v>
+        <v>565029</v>
       </c>
       <c r="R51" t="n">
-        <v>7060982</v>
+        <v>7061081</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5987,11 +5573,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6018,10 +5599,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132126749</v>
+        <v>119204924</v>
       </c>
       <c r="B52" t="n">
-        <v>79329</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6029,37 +5610,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>564932</v>
+        <v>565083</v>
       </c>
       <c r="R52" t="n">
-        <v>7061188</v>
+        <v>7061046</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6083,12 +5664,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6103,65 +5694,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132123934</v>
+        <v>119204967</v>
       </c>
       <c r="B53" t="n">
-        <v>58058</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>565249</v>
+        <v>565052</v>
       </c>
       <c r="R53" t="n">
-        <v>7061060</v>
+        <v>7061050</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6185,12 +5771,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6205,22 +5801,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132123303</v>
+        <v>119219136</v>
       </c>
       <c r="B54" t="n">
-        <v>57954</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6228,42 +5824,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>565329</v>
+        <v>565028</v>
       </c>
       <c r="R54" t="n">
-        <v>7061011</v>
+        <v>7061042</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6287,17 +5878,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6312,22 +5898,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132124552</v>
+        <v>119219137</v>
       </c>
       <c r="B55" t="n">
-        <v>79329</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6335,37 +5921,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Ottran, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>565189</v>
+        <v>565042</v>
       </c>
       <c r="R55" t="n">
-        <v>7061025</v>
+        <v>7061038</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6389,12 +5975,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6409,57 +5995,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132120301</v>
+        <v>132126630</v>
       </c>
       <c r="B56" t="n">
-        <v>92373</v>
+        <v>79130</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1209</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>565389</v>
+        <v>564965</v>
       </c>
       <c r="R56" t="n">
-        <v>7061042</v>
+        <v>7061169</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6518,10 +6104,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132122995</v>
+        <v>119204357</v>
       </c>
       <c r="B57" t="n">
-        <v>83177</v>
+        <v>79946</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6529,21 +6115,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6553,13 +6139,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>565282</v>
+        <v>565153</v>
       </c>
       <c r="R57" t="n">
-        <v>7061075</v>
+        <v>7060971</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6583,22 +6169,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6613,22 +6199,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Hillevi Nydahl</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132122582</v>
+        <v>119204963</v>
       </c>
       <c r="B58" t="n">
-        <v>58115</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6636,43 +6222,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>565332</v>
+        <v>565053</v>
       </c>
       <c r="R58" t="n">
-        <v>7061108</v>
+        <v>7061049</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6699,22 +6276,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6729,22 +6306,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132121251</v>
+        <v>132127620</v>
       </c>
       <c r="B59" t="n">
-        <v>79329</v>
+        <v>79992</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6752,21 +6329,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6776,13 +6353,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>565427</v>
+        <v>565100</v>
       </c>
       <c r="R59" t="n">
-        <v>7061070</v>
+        <v>7061058</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6809,19 +6386,9 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6836,22 +6403,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132124232</v>
+        <v>119204198</v>
       </c>
       <c r="B60" t="n">
-        <v>57954</v>
+        <v>80432</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6859,42 +6426,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>565218</v>
+        <v>565199</v>
       </c>
       <c r="R60" t="n">
-        <v>7061030</v>
+        <v>7060964</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6918,17 +6480,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6943,22 +6510,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132126693</v>
+        <v>132123448</v>
       </c>
       <c r="B61" t="n">
-        <v>91913</v>
+        <v>80488</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6966,34 +6533,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>564952</v>
+        <v>565433</v>
       </c>
       <c r="R61" t="n">
-        <v>7061172</v>
+        <v>7060997</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7052,50 +6619,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>132124733</v>
+        <v>132123482</v>
       </c>
       <c r="B62" t="n">
-        <v>57954</v>
+        <v>80493</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>565156</v>
+        <v>565432</v>
       </c>
       <c r="R62" t="n">
-        <v>7061023</v>
+        <v>7061006</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7128,11 +6690,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Färska ringhack tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7159,48 +6716,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>132126475</v>
+        <v>119204231</v>
       </c>
       <c r="B63" t="n">
-        <v>79329</v>
+        <v>80468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>564979</v>
+        <v>565199</v>
       </c>
       <c r="R63" t="n">
-        <v>7061150</v>
+        <v>7060966</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7224,12 +6781,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7244,60 +6811,65 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132126630</v>
+        <v>119204908</v>
       </c>
       <c r="B64" t="n">
-        <v>79086</v>
+        <v>57950</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>564965</v>
+        <v>565046</v>
       </c>
       <c r="R64" t="n">
-        <v>7061169</v>
+        <v>7061046</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7321,12 +6893,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7353,45 +6925,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>132120471</v>
+        <v>132126393</v>
       </c>
       <c r="B65" t="n">
-        <v>92212</v>
+        <v>57972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>565365</v>
+        <v>564986</v>
       </c>
       <c r="R65" t="n">
-        <v>7061069</v>
+        <v>7061138</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7450,27 +7027,27 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>132121811</v>
+        <v>132127502</v>
       </c>
       <c r="B66" t="n">
-        <v>57954</v>
+        <v>57972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -7481,7 +7058,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7490,13 +7067,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>565428</v>
+        <v>565078</v>
       </c>
       <c r="R66" t="n">
-        <v>7061153</v>
+        <v>7061092</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7523,24 +7100,9 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7555,22 +7117,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>132123240</v>
+        <v>118621670</v>
       </c>
       <c r="B67" t="n">
-        <v>57954</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7598,7 +7160,7 @@
       <c r="I67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7607,10 +7169,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>565294</v>
+        <v>565247</v>
       </c>
       <c r="R67" t="n">
-        <v>7061033</v>
+        <v>7061001</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7637,27 +7199,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7684,10 +7241,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>132122939</v>
+        <v>118621853</v>
       </c>
       <c r="B68" t="n">
-        <v>83311</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7695,37 +7252,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>565315</v>
+        <v>565182</v>
       </c>
       <c r="R68" t="n">
-        <v>7061039</v>
+        <v>7060974</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7749,12 +7311,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7769,22 +7341,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>132127468</v>
+        <v>118621891</v>
       </c>
       <c r="B69" t="n">
-        <v>79329</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7792,37 +7364,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>565050</v>
+        <v>565134</v>
       </c>
       <c r="R69" t="n">
-        <v>7061109</v>
+        <v>7060977</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7846,12 +7423,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7866,22 +7453,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>132121002</v>
+        <v>118621901</v>
       </c>
       <c r="B70" t="n">
-        <v>83311</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7889,37 +7476,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>565348</v>
+        <v>565130</v>
       </c>
       <c r="R70" t="n">
-        <v>7061074</v>
+        <v>7060967</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7943,12 +7535,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7963,22 +7565,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132126348</v>
+        <v>118621971</v>
       </c>
       <c r="B71" t="n">
-        <v>79329</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7986,37 +7588,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>564994</v>
+        <v>565098</v>
       </c>
       <c r="R71" t="n">
-        <v>7061131</v>
+        <v>7060988</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8040,12 +7647,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>22:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8060,22 +7677,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132126227</v>
+        <v>118623242</v>
       </c>
       <c r="B72" t="n">
-        <v>57954</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8108,17 +7725,17 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>564995</v>
+        <v>565428</v>
       </c>
       <c r="R72" t="n">
-        <v>7061131</v>
+        <v>7060941</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8142,17 +7759,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>23:42</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>23:42</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8167,22 +7789,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>132124500</v>
+        <v>118623299</v>
       </c>
       <c r="B73" t="n">
-        <v>57954</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8210,7 +7832,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8219,13 +7841,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>565187</v>
+        <v>565430</v>
       </c>
       <c r="R73" t="n">
-        <v>7061027</v>
+        <v>7061018</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8249,17 +7871,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack gran</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>23:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8274,22 +7901,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>132127354</v>
+        <v>118623324</v>
       </c>
       <c r="B74" t="n">
-        <v>79329</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8297,37 +7924,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>565022</v>
+        <v>565410</v>
       </c>
       <c r="R74" t="n">
-        <v>7061116</v>
+        <v>7061035</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8351,12 +7983,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>23:50</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8371,22 +8013,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132121965</v>
+        <v>119149694</v>
       </c>
       <c r="B75" t="n">
-        <v>79329</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8394,37 +8036,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>565402</v>
+        <v>565380</v>
       </c>
       <c r="R75" t="n">
-        <v>7061164</v>
+        <v>7061004</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8448,12 +8095,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8468,22 +8125,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132127580</v>
+        <v>119149743</v>
       </c>
       <c r="B76" t="n">
-        <v>57954</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8511,7 +8168,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8520,13 +8177,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>565084</v>
+        <v>565387</v>
       </c>
       <c r="R76" t="n">
-        <v>7061073</v>
+        <v>7061007</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8550,17 +8207,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack, tall</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8575,22 +8237,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132123094</v>
+        <v>119204425</v>
       </c>
       <c r="B77" t="n">
-        <v>57954</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8616,24 +8278,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>565285</v>
+        <v>565136</v>
       </c>
       <c r="R77" t="n">
-        <v>7061041</v>
+        <v>7060972</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8657,17 +8314,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8682,22 +8344,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132120892</v>
+        <v>119204938</v>
       </c>
       <c r="B78" t="n">
-        <v>58115</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8705,31 +8367,27 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8738,13 +8396,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>565374</v>
+        <v>565056</v>
       </c>
       <c r="R78" t="n">
-        <v>7061087</v>
+        <v>7061039</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8768,22 +8426,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8798,22 +8446,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132122865</v>
+        <v>119205327</v>
       </c>
       <c r="B79" t="n">
-        <v>79329</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8821,37 +8469,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>565271</v>
+        <v>565047</v>
       </c>
       <c r="R79" t="n">
-        <v>7061139</v>
+        <v>7061046</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8875,12 +8528,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,22 +8558,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132127620</v>
+        <v>132121523</v>
       </c>
       <c r="B80" t="n">
-        <v>79948</v>
+        <v>57975</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8918,37 +8581,46 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>565100</v>
+        <v>565420</v>
       </c>
       <c r="R80" t="n">
-        <v>7061058</v>
+        <v>7061119</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8975,9 +8647,19 @@
           <t>2026-04-02</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8992,22 +8674,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132125187</v>
+        <v>132121811</v>
       </c>
       <c r="B81" t="n">
-        <v>83311</v>
+        <v>57975</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9015,37 +8697,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>565029</v>
+        <v>565428</v>
       </c>
       <c r="R81" t="n">
-        <v>7061081</v>
+        <v>7061153</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9072,9 +8759,24 @@
           <t>2026-04-02</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9089,22 +8791,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132125044</v>
+        <v>132123094</v>
       </c>
       <c r="B82" t="n">
-        <v>79329</v>
+        <v>57975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9112,34 +8814,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>565041</v>
+        <v>565285</v>
       </c>
       <c r="R82" t="n">
-        <v>7061062</v>
+        <v>7061041</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9172,6 +8879,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9198,10 +8910,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132126890</v>
+        <v>132123180</v>
       </c>
       <c r="B83" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9234,14 +8946,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>565000</v>
+        <v>565295</v>
       </c>
       <c r="R83" t="n">
-        <v>7061164</v>
+        <v>7061029</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9278,7 +8990,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Färska ringhack, tall</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9305,10 +9017,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132122130</v>
+        <v>132123234</v>
       </c>
       <c r="B84" t="n">
-        <v>79329</v>
+        <v>57975</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9316,34 +9028,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>565382</v>
+        <v>565315</v>
       </c>
       <c r="R84" t="n">
-        <v>7061115</v>
+        <v>7061025</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9376,6 +9093,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9402,10 +9124,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>132127097</v>
+        <v>132123240</v>
       </c>
       <c r="B85" t="n">
-        <v>79329</v>
+        <v>57975</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9413,37 +9135,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>565020</v>
+        <v>565294</v>
       </c>
       <c r="R85" t="n">
-        <v>7061146</v>
+        <v>7061033</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9470,9 +9197,24 @@
           <t>2026-04-02</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9487,22 +9229,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132126393</v>
+        <v>132123303</v>
       </c>
       <c r="B86" t="n">
-        <v>57951</v>
+        <v>57975</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9510,16 +9252,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9530,19 +9272,19 @@
       <c r="I86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>564986</v>
+        <v>565329</v>
       </c>
       <c r="R86" t="n">
-        <v>7061138</v>
+        <v>7061011</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9575,6 +9317,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9601,10 +9348,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132120876</v>
+        <v>132123395</v>
       </c>
       <c r="B87" t="n">
-        <v>79329</v>
+        <v>57975</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9612,34 +9359,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>565379</v>
+        <v>565388</v>
       </c>
       <c r="R87" t="n">
-        <v>7061167</v>
+        <v>7060982</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9672,6 +9424,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9698,10 +9455,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132125526</v>
+        <v>132123408</v>
       </c>
       <c r="B88" t="n">
-        <v>79329</v>
+        <v>57975</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9709,34 +9466,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>564999</v>
+        <v>565387</v>
       </c>
       <c r="R88" t="n">
-        <v>7061122</v>
+        <v>7060982</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9769,6 +9531,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9795,10 +9562,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132129630</v>
+        <v>132124232</v>
       </c>
       <c r="B89" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9826,7 +9593,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9835,10 +9602,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>565290</v>
+        <v>565218</v>
       </c>
       <c r="R89" t="n">
-        <v>7061052</v>
+        <v>7061030</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -9875,7 +9642,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Födosökte på gran-gren</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9902,48 +9669,53 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132120483</v>
+        <v>132124476</v>
       </c>
       <c r="B90" t="n">
-        <v>92373</v>
+        <v>57975</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>565376</v>
+        <v>565183</v>
       </c>
       <c r="R90" t="n">
-        <v>7061044</v>
+        <v>7061007</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9970,9 +9742,24 @@
           <t>2026-04-02</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9987,22 +9774,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132120238</v>
+        <v>132124500</v>
       </c>
       <c r="B91" t="n">
-        <v>91913</v>
+        <v>57975</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10010,34 +9797,39 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>565382</v>
+        <v>565187</v>
       </c>
       <c r="R91" t="n">
-        <v>7061041</v>
+        <v>7061027</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10070,6 +9862,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Färska ringhack gran</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10096,10 +9893,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>132126937</v>
+        <v>132124733</v>
       </c>
       <c r="B92" t="n">
-        <v>79329</v>
+        <v>57975</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10107,34 +9904,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
+          <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>565003</v>
+        <v>565156</v>
       </c>
       <c r="R92" t="n">
-        <v>7061162</v>
+        <v>7061023</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10167,6 +9969,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10193,10 +10000,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>132121843</v>
+        <v>132126227</v>
       </c>
       <c r="B93" t="n">
-        <v>79329</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10204,37 +10011,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>565430</v>
+        <v>564995</v>
       </c>
       <c r="R93" t="n">
-        <v>7061164</v>
+        <v>7061131</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10261,19 +10073,14 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:14</t>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10288,62 +10095,62 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>132121206</v>
+        <v>132126890</v>
       </c>
       <c r="B94" t="n">
-        <v>57142</v>
+        <v>57975</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ottran, Ottran, Ång</t>
+          <t>Gamm-Vängelflon, Gamm-Vängelflon, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>565326</v>
+        <v>565000</v>
       </c>
       <c r="R94" t="n">
-        <v>7061086</v>
+        <v>7061164</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10376,6 +10183,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10402,10 +10214,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>132120233</v>
+        <v>132127580</v>
       </c>
       <c r="B95" t="n">
-        <v>92212</v>
+        <v>57975</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10413,34 +10225,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ottran, Ottran, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>565380</v>
+        <v>565084</v>
       </c>
       <c r="R95" t="n">
-        <v>7061037</v>
+        <v>7061073</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10473,6 +10290,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10499,10 +10321,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>132124476</v>
+        <v>132127761</v>
       </c>
       <c r="B96" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10539,13 +10361,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>565183</v>
+        <v>565110</v>
       </c>
       <c r="R96" t="n">
-        <v>7061007</v>
+        <v>7061072</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10572,24 +10394,14 @@
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska ringhack, tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10604,15 +10416,1305 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>132129630</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>565290</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7061052</v>
+      </c>
+      <c r="S97" t="n">
+        <v>15</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Födosökte på gran-gren</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>132130749</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>565183</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7061054</v>
+      </c>
+      <c r="S98" t="n">
+        <v>15</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>132121206</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>565326</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7061086</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>119149922</v>
+      </c>
+      <c r="B100" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>565412</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7060929</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>21:23</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
+      <c r="AX100" t="inlineStr">
         <is>
           <t>Kim Hultgren</t>
         </is>
       </c>
-      <c r="AY96" t="inlineStr"/>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>132120892</v>
+      </c>
+      <c r="B101" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>565374</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7061087</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>132122582</v>
+      </c>
+      <c r="B102" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>565332</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7061108</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>132120679</v>
+      </c>
+      <c r="B103" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>565353</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7061036</v>
+      </c>
+      <c r="S103" t="n">
+        <v>15</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>132123934</v>
+      </c>
+      <c r="B104" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>565249</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7061060</v>
+      </c>
+      <c r="S104" t="n">
+        <v>15</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>119204501</v>
+      </c>
+      <c r="B105" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>565147</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7060991</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>119205818</v>
+      </c>
+      <c r="B106" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>565011</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7060911</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>119203767</v>
+      </c>
+      <c r="B107" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>565206</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7061027</v>
+      </c>
+      <c r="S107" t="n">
+        <v>20</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>119203918</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Ottran, Ottran, Ång</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>565151</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7061004</v>
+      </c>
+      <c r="S108" t="n">
+        <v>20</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26948-2024 artfynd.xlsx
+++ b/artfynd/A 26948-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AZ108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204686</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120233</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120471</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120206</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120238</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120493</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126693</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120301</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120483</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122995</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127333</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219132</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119208820</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219142</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219143</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119203593</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119203597</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2458,6 +2548,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219135</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2565,6 +2660,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204162</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2662,6 +2762,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204561</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2759,6 +2864,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204873</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2860,6 +2970,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119213719</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2957,6 +3072,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120876</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3064,6 +3184,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132121251</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3171,6 +3296,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132121843</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3268,6 +3398,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132121965</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3365,6 +3500,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122130</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3462,6 +3602,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122865</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3559,6 +3704,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123121</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3656,6 +3806,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132124552</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3753,6 +3908,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132125044</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3850,6 +4010,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132125276</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3947,6 +4112,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132125526</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4044,6 +4214,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126348</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4141,6 +4316,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126475</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4238,6 +4418,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126678</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4335,6 +4520,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126749</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4432,6 +4622,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126937</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4529,6 +4724,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127049</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4626,6 +4826,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127097</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4723,6 +4928,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127354</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4820,6 +5030,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127468</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4917,6 +5132,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127840</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5014,6 +5234,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127939</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5111,6 +5336,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132128016</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5208,6 +5438,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132128160</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5305,6 +5540,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132121002</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5402,6 +5642,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132121316</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5499,6 +5744,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122939</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5596,6 +5846,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132125187</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5703,6 +5958,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204924</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5810,6 +6070,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204967</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5907,6 +6172,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219136</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6004,6 +6274,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119219137</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6101,6 +6376,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126630</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6208,6 +6488,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204357</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6315,6 +6600,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204963</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6412,6 +6702,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127620</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6519,6 +6814,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204198</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6616,6 +6916,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123448</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6713,6 +7018,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123482</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6820,6 +7130,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204231</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6922,6 +7237,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204908</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7024,6 +7344,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126393</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7126,6 +7451,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127502</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7238,6 +7568,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118621670</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7350,6 +7685,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118621853</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7462,6 +7802,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118621891</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7574,6 +7919,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118621901</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7686,6 +8036,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118621971</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7798,6 +8153,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118623242</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7910,6 +8270,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118623299</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8022,6 +8387,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118623324</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8134,6 +8504,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119149694</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8246,6 +8621,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119149743</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8353,6 +8733,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204425</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8455,6 +8840,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204938</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8567,6 +8957,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119205327</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8683,6 +9078,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132121523</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8800,6 +9200,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132121811</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8907,6 +9312,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123094</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9014,6 +9424,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123180</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9121,6 +9536,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123234</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9238,6 +9658,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123240</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9345,6 +9770,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123303</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9452,6 +9882,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123395</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9559,6 +9994,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123408</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9666,6 +10106,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132124232</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9783,6 +10228,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132124476</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9890,6 +10340,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132124500</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9997,6 +10452,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132124733</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10104,6 +10564,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126227</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10211,6 +10676,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132126890</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10318,6 +10788,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127580</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10425,6 +10900,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132127761</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10532,6 +11012,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132129630</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10639,6 +11124,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132130749</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10741,6 +11231,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132121206</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10857,6 +11352,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119149922</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10973,6 +11473,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120892</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11089,6 +11594,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132122582</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11195,6 +11705,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132120679</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11297,6 +11812,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132123934</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11404,6 +11924,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119204501</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11511,6 +12036,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119205818</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11618,6 +12148,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119203767</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11715,8 +12250,122 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119203918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>